--- a/data/trans_orig/P1402-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2007</t>
+          <t>Población con diagnóstico de diabetes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35975</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42386</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437801</t>
+          <t>437434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457139</t>
+          <t>457634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294102</t>
+          <t>293518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304482</t>
+          <t>304066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738071</t>
+          <t>735822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>760137</t>
+          <t>759131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37742</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340242</t>
+          <t>340509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355660</t>
+          <t>355934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355287</t>
+          <t>355065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368602</t>
+          <t>368489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701057</t>
+          <t>700657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721362</t>
+          <t>721280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>37423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>22085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>28904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53718</t>
+          <t>54060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502719</t>
+          <t>504966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522953</t>
+          <t>524129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146464</t>
+          <t>145697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160530</t>
+          <t>159998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656453</t>
+          <t>656111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680539</t>
+          <t>681267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75140</t>
+          <t>76651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114882</t>
+          <t>113380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45890</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107847</t>
+          <t>105467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149232</t>
+          <t>149354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1123452</t>
+          <t>1124954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1163194</t>
+          <t>1161683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668395</t>
+          <t>668380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>690289</t>
+          <t>690530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1803388</t>
+          <t>1803266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1844773</t>
+          <t>1847153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33118</t>
+          <t>31743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48565</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>43286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74915</t>
+          <t>73399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317437</t>
+          <t>318812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335796</t>
+          <t>336824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520187</t>
+          <t>519866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>544545</t>
+          <t>543659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>844392</t>
+          <t>845908</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875283</t>
+          <t>876021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111642</t>
+          <t>112425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>156056</t>
+          <t>155272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109917</t>
+          <t>111836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155208</t>
+          <t>155577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1092704</t>
+          <t>1093488</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1137118</t>
+          <t>1136335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1391752</t>
+          <t>1391383</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1437043</t>
+          <t>1435124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161167</t>
+          <t>160878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211645</t>
+          <t>212394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202437</t>
+          <t>201098</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>260780</t>
+          <t>255999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>377066</t>
+          <t>375225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455313</t>
+          <t>453100</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3058545</t>
+          <t>3057796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3109023</t>
+          <t>3109312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3117344</t>
+          <t>3122125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3175687</t>
+          <t>3177026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6193001</t>
+          <t>6195214</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6271248</t>
+          <t>6273089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2012</t>
+          <t>Población con diagnóstico de diabetes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39566</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409852</t>
+          <t>409776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427297</t>
+          <t>426906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294866</t>
+          <t>294553</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309111</t>
+          <t>309279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712099</t>
+          <t>710223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>732590</t>
+          <t>733171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>33186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45149</t>
+          <t>45312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385901</t>
+          <t>385611</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404344</t>
+          <t>404479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320360</t>
+          <t>320240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>333985</t>
+          <t>333893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711659</t>
+          <t>711496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735150</t>
+          <t>734123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55809</t>
+          <t>56571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88888</t>
+          <t>89061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26339</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71480</t>
+          <t>70259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108365</t>
+          <t>107328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540527</t>
+          <t>540354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>573606</t>
+          <t>572844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233790</t>
+          <t>235072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250641</t>
+          <t>251051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>781179</t>
+          <t>782216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818064</t>
+          <t>819285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85613</t>
+          <t>84459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124806</t>
+          <t>125289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>56848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125790</t>
+          <t>122215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172675</t>
+          <t>169995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1034203</t>
+          <t>1033720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1073396</t>
+          <t>1074550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706604</t>
+          <t>707874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733958</t>
+          <t>733981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1751056</t>
+          <t>1753736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1797941</t>
+          <t>1801516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48864</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>56594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88023</t>
+          <t>89123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133266</t>
+          <t>130660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461732</t>
+          <t>461336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485812</t>
+          <t>484975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>672223</t>
+          <t>671123</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703075</t>
+          <t>703652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1137577</t>
+          <t>1140183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1181113</t>
+          <t>1180359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131613</t>
+          <t>135025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179376</t>
+          <t>180729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137684</t>
+          <t>135879</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185699</t>
+          <t>186175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253507</t>
+          <t>253525</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264933</t>
+          <t>264994</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>929975</t>
+          <t>928622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>977738</t>
+          <t>974326</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1190534</t>
+          <t>1190058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1238549</t>
+          <t>1240354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228918</t>
+          <t>225395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>292523</t>
+          <t>288486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>275175</t>
+          <t>274590</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>343125</t>
+          <t>341638</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>519494</t>
+          <t>517498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>614160</t>
+          <t>607513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3129387</t>
+          <t>3133424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3192992</t>
+          <t>3196515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3203790</t>
+          <t>3205277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3271740</t>
+          <t>3272325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6354665</t>
+          <t>6361312</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6449331</t>
+          <t>6451327</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2016</t>
+          <t>Población con diagnóstico de diabetes en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44849</t>
+          <t>46364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62240</t>
+          <t>62765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384243</t>
+          <t>382728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>406678</t>
+          <t>407191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>321165</t>
+          <t>320729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337146</t>
+          <t>337315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713907</t>
+          <t>713382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>740914</t>
+          <t>740990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38392</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51910</t>
+          <t>53968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338835</t>
+          <t>339749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358333</t>
+          <t>358941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352017</t>
+          <t>351142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367641</t>
+          <t>366753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697590</t>
+          <t>695532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722211</t>
+          <t>722555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69375</t>
+          <t>69484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>18042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49052</t>
+          <t>49490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80672</t>
+          <t>79095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452539</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481188</t>
+          <t>480717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147682</t>
+          <t>148081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161284</t>
+          <t>161360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607364</t>
+          <t>608941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638984</t>
+          <t>638546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92211</t>
+          <t>92327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133053</t>
+          <t>132385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46655</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123411</t>
+          <t>125407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168490</t>
+          <t>169619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1016585</t>
+          <t>1017253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1057427</t>
+          <t>1057311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>779221</t>
+          <t>780413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>803368</t>
+          <t>803108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1807024</t>
+          <t>1805895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1852103</t>
+          <t>1850107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55417</t>
+          <t>54997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86970</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56799</t>
+          <t>56248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92508</t>
+          <t>88198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120121</t>
+          <t>120240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165143</t>
+          <t>164600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>533736</t>
+          <t>533607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>565289</t>
+          <t>565709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>645736</t>
+          <t>650046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>681445</t>
+          <t>681996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1193807</t>
+          <t>1194350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238829</t>
+          <t>1238710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132139</t>
+          <t>131349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>181620</t>
+          <t>182129</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>134693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183252</t>
+          <t>185686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277295</t>
+          <t>276380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286068</t>
+          <t>286009</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>900405</t>
+          <t>899896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>949886</t>
+          <t>950676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1185918</t>
+          <t>1183484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1235142</t>
+          <t>1234477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>267069</t>
+          <t>266782</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>331379</t>
+          <t>330684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>260532</t>
+          <t>263662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>332562</t>
+          <t>333043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>549112</t>
+          <t>548347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>644603</t>
+          <t>642598</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3054343</t>
+          <t>3055038</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3118653</t>
+          <t>3118940</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3199034</t>
+          <t>3198553</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3271064</t>
+          <t>3267934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6272715</t>
+          <t>6274720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6368206</t>
+          <t>6368971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2023</t>
+          <t>Población con diagnóstico de diabetes en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21396</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47850</t>
+          <t>47312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73169</t>
+          <t>73978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444982</t>
+          <t>446119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470403</t>
+          <t>471315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425490</t>
+          <t>426060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436805</t>
+          <t>437567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>878929</t>
+          <t>878120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>904248</t>
+          <t>904786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54730</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>39191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>64370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397483</t>
+          <t>399720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420378</t>
+          <t>421224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367934</t>
+          <t>367705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376734</t>
+          <t>376546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>770368</t>
+          <t>769754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794670</t>
+          <t>794933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86807</t>
+          <t>87278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580738</t>
+          <t>580267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647456</t>
+          <t>649233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143749</t>
+          <t>143081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155332</t>
+          <t>154777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>732557</t>
+          <t>733945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>808066</t>
+          <t>807117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97757</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135488</t>
+          <t>133742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22874</t>
+          <t>24568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63105</t>
+          <t>63574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110330</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190999</t>
+          <t>190506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897974</t>
+          <t>899720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935705</t>
+          <t>935656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>914989</t>
+          <t>914520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>955220</t>
+          <t>953526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1820557</t>
+          <t>1821050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1901226</t>
+          <t>1897320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33740</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54595</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63875</t>
+          <t>64322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103952</t>
+          <t>104010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106548</t>
+          <t>105914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150060</t>
+          <t>150196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418580</t>
+          <t>418065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>439435</t>
+          <t>439931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>735044</t>
+          <t>734986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>775121</t>
+          <t>774674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1162111</t>
+          <t>1161975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1205623</t>
+          <t>1206257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>75213</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101354</t>
+          <t>101671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77593</t>
+          <t>76020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>104338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233813</t>
+          <t>234430</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240025</t>
+          <t>240026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>658940</t>
+          <t>658623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>685190</t>
+          <t>685081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>895928</t>
+          <t>896463</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>923208</t>
+          <t>924781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>229993</t>
+          <t>233959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>337602</t>
+          <t>338637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214600</t>
+          <t>207779</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>292705</t>
+          <t>291511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>484046</t>
+          <t>483359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>614244</t>
+          <t>611701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3034512</t>
+          <t>3033477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3142121</t>
+          <t>3138155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3280386</t>
+          <t>3281580</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3358491</t>
+          <t>3365312</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6330961</t>
+          <t>6333504</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6461159</t>
+          <t>6461846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1402-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>36021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437434</t>
+          <t>437755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457634</t>
+          <t>457971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293518</t>
+          <t>294692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304066</t>
+          <t>304052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735822</t>
+          <t>738151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759131</t>
+          <t>759752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26914</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>17834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>37696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340509</t>
+          <t>340020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355934</t>
+          <t>355885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355065</t>
+          <t>354031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368489</t>
+          <t>368513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700657</t>
+          <t>701103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721280</t>
+          <t>720585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54060</t>
+          <t>55395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504966</t>
+          <t>503664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524129</t>
+          <t>523141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145697</t>
+          <t>145544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159998</t>
+          <t>160265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656111</t>
+          <t>654776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681267</t>
+          <t>679350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76651</t>
+          <t>76830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113380</t>
+          <t>111722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105467</t>
+          <t>105447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149354</t>
+          <t>148688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1124954</t>
+          <t>1126612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1161683</t>
+          <t>1161504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668380</t>
+          <t>669154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>690530</t>
+          <t>691084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1803266</t>
+          <t>1803932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1847153</t>
+          <t>1847173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31743</t>
+          <t>33646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48886</t>
+          <t>48668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43286</t>
+          <t>43504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73399</t>
+          <t>72505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>318812</t>
+          <t>316909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336824</t>
+          <t>335633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>519866</t>
+          <t>520084</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>543659</t>
+          <t>543717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845908</t>
+          <t>846802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876021</t>
+          <t>875803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112425</t>
+          <t>112959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>155272</t>
+          <t>154765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111836</t>
+          <t>113444</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155577</t>
+          <t>157019</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1093488</t>
+          <t>1093995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1136335</t>
+          <t>1135801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1391383</t>
+          <t>1389941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1435124</t>
+          <t>1433516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160878</t>
+          <t>162122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212394</t>
+          <t>214061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>201098</t>
+          <t>201810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>255999</t>
+          <t>258740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375225</t>
+          <t>376343</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>453100</t>
+          <t>458066</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3057796</t>
+          <t>3056129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3109312</t>
+          <t>3108068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3122125</t>
+          <t>3119384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3177026</t>
+          <t>3176314</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6195214</t>
+          <t>6190248</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6273089</t>
+          <t>6271971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41442</t>
+          <t>42834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409776</t>
+          <t>410149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426906</t>
+          <t>427158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294553</t>
+          <t>295266</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309279</t>
+          <t>309260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>710223</t>
+          <t>708831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>733171</t>
+          <t>732244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45312</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385611</t>
+          <t>385143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404479</t>
+          <t>404909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320240</t>
+          <t>321025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>333893</t>
+          <t>333767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711496</t>
+          <t>711299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734123</t>
+          <t>734883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56571</t>
+          <t>58412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89061</t>
+          <t>91599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70259</t>
+          <t>70611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107328</t>
+          <t>109365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540354</t>
+          <t>537816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>572844</t>
+          <t>571003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235072</t>
+          <t>235725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251051</t>
+          <t>250356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>782216</t>
+          <t>780179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819285</t>
+          <t>818933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84459</t>
+          <t>84577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125289</t>
+          <t>124972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30741</t>
+          <t>31799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56848</t>
+          <t>59273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122215</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169995</t>
+          <t>174395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1033720</t>
+          <t>1034037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1074550</t>
+          <t>1074432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>707874</t>
+          <t>705449</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733981</t>
+          <t>732923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1753736</t>
+          <t>1749336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1801516</t>
+          <t>1799550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>50077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56594</t>
+          <t>56487</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89123</t>
+          <t>90122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90484</t>
+          <t>89180</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130660</t>
+          <t>130404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461336</t>
+          <t>460519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484975</t>
+          <t>485932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>671123</t>
+          <t>670124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703652</t>
+          <t>703759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1140183</t>
+          <t>1140439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1180359</t>
+          <t>1181663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135025</t>
+          <t>134464</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180729</t>
+          <t>180459</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135879</t>
+          <t>134971</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186175</t>
+          <t>188681</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253525</t>
+          <t>253515</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264994</t>
+          <t>264909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>928622</t>
+          <t>928892</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>974326</t>
+          <t>974887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1190058</t>
+          <t>1187552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1240354</t>
+          <t>1241262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>225395</t>
+          <t>227395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>288486</t>
+          <t>292993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>274590</t>
+          <t>273147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>341638</t>
+          <t>340578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>517498</t>
+          <t>518142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>607513</t>
+          <t>611216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3133424</t>
+          <t>3128917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3196515</t>
+          <t>3194515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3205277</t>
+          <t>3206337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3272325</t>
+          <t>3273768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6361312</t>
+          <t>6357609</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6451327</t>
+          <t>6450683</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>44757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35157</t>
+          <t>36189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62765</t>
+          <t>64400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382728</t>
+          <t>384335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407191</t>
+          <t>407609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320729</t>
+          <t>322010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337315</t>
+          <t>337612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713382</t>
+          <t>711747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>740990</t>
+          <t>739958</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37478</t>
+          <t>38833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339749</t>
+          <t>338394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358941</t>
+          <t>358673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351142</t>
+          <t>351802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366753</t>
+          <t>366778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>695532</t>
+          <t>698336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722555</t>
+          <t>722468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41197</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69484</t>
+          <t>69668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49490</t>
+          <t>50619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79095</t>
+          <t>81557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>452246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480717</t>
+          <t>481166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148081</t>
+          <t>147453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161360</t>
+          <t>161552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>608941</t>
+          <t>606479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638546</t>
+          <t>637417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92327</t>
+          <t>95006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132385</t>
+          <t>136421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>46412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125407</t>
+          <t>121956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169619</t>
+          <t>169210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1017253</t>
+          <t>1013217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1057311</t>
+          <t>1054632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>780413</t>
+          <t>779464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>803108</t>
+          <t>802960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1805895</t>
+          <t>1806304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1850107</t>
+          <t>1853558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54997</t>
+          <t>55591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>86569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56248</t>
+          <t>55813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88198</t>
+          <t>89292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120240</t>
+          <t>118895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164600</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>533607</t>
+          <t>534137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>565709</t>
+          <t>565115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>650046</t>
+          <t>648952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>681996</t>
+          <t>682431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1194350</t>
+          <t>1195663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238710</t>
+          <t>1240055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131349</t>
+          <t>130548</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182129</t>
+          <t>179479</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>134630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185686</t>
+          <t>185914</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276380</t>
+          <t>277747</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286009</t>
+          <t>286023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>899896</t>
+          <t>902546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>950676</t>
+          <t>951477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1183484</t>
+          <t>1183256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1234477</t>
+          <t>1234540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>266782</t>
+          <t>267947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>330684</t>
+          <t>333328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>263662</t>
+          <t>264587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>333043</t>
+          <t>334338</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>548347</t>
+          <t>548735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>642598</t>
+          <t>644076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3055038</t>
+          <t>3052394</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3118940</t>
+          <t>3117775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3198553</t>
+          <t>3197258</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3267934</t>
+          <t>3267009</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6274720</t>
+          <t>6273242</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6368971</t>
+          <t>6368583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45378</t>
+          <t>49934</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>39126</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59093</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59794</t>
+          <t>65938</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>53022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73978</t>
+          <t>81460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>459834</t>
+          <t>500684</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446119</t>
+          <t>485737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471315</t>
+          <t>511492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>432470</t>
+          <t>471723</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426060</t>
+          <t>464056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>437567</t>
+          <t>476656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>892304</t>
+          <t>972407</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>878120</t>
+          <t>956885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>904786</t>
+          <t>985323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446886</t>
+          <t>487727</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446886</t>
+          <t>487727</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446886</t>
+          <t>487727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952098</t>
+          <t>1038345</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952098</t>
+          <t>1038345</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952098</t>
+          <t>1038345</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>30450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52493</t>
+          <t>53397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>65969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>411103</t>
+          <t>441445</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399720</t>
+          <t>429815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421224</t>
+          <t>452762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>372745</t>
+          <t>412257</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367705</t>
+          <t>406665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376546</t>
+          <t>416160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>783847</t>
+          <t>853702</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>769754</t>
+          <t>839735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794933</t>
+          <t>864761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51295</t>
+          <t>53992</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>41869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>66029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68237</t>
+          <t>72751</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100511</t>
+          <t>88506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>616250</t>
+          <t>416751</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580267</t>
+          <t>404714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649233</t>
+          <t>428874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149970</t>
+          <t>168737</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143081</t>
+          <t>161990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154777</t>
+          <t>174597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>766219</t>
+          <t>585490</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733945</t>
+          <t>569735</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>807117</t>
+          <t>598501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>129958</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97806</t>
+          <t>112399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133742</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46215</t>
+          <t>51380</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24568</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63574</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>161620</t>
+          <t>181338</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114236</t>
+          <t>159006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190506</t>
+          <t>205937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>918058</t>
+          <t>1000321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>899720</t>
+          <t>980322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935656</t>
+          <t>1017880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>931879</t>
+          <t>809831</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>914520</t>
+          <t>798654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>953526</t>
+          <t>819770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1849936</t>
+          <t>1810152</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1821050</t>
+          <t>1785553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897320</t>
+          <t>1832484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033462</t>
+          <t>1130279</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033462</t>
+          <t>1130279</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033462</t>
+          <t>1130279</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011556</t>
+          <t>1991490</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011556</t>
+          <t>1991490</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011556</t>
+          <t>1991490</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43088</t>
+          <t>48280</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>38081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,67 +10040,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>86344</t>
+          <t>95399</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64322</t>
+          <t>80901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104010</t>
+          <t>109474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>143679</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>127442</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>161298</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>10,29%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>129432</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>105914</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>150196</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>430087</t>
+          <t>517640</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418065</t>
+          <t>504340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>439931</t>
+          <t>527839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,67 +10153,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>752652</t>
+          <t>734728</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734986</t>
+          <t>720653</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>774674</t>
+          <t>749226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>88,51%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1252369</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1234750</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1268606</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>89,71%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>87,6%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1182739</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1161975</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1206257</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>565920</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>565920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>565920</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312171</t>
+          <t>1396048</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312171</t>
+          <t>1396048</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312171</t>
+          <t>1396048</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,27 +10348,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>87933</t>
+          <t>96095</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75213</t>
+          <t>83573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101671</t>
+          <t>110793</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>89954</t>
+          <t>98109</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76020</t>
+          <t>84185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104338</t>
+          <t>115662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -10461,22 +10461,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>238486</t>
+          <t>235214</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234430</t>
+          <t>231222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240026</t>
+          <t>236692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>672361</t>
+          <t>747100</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>658623</t>
+          <t>732402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>685081</t>
+          <t>759622</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>910847</t>
+          <t>982314</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>896463</t>
+          <t>964761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>924781</t>
+          <t>996238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>298297</t>
+          <t>325945</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>233959</t>
+          <t>296272</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>338637</t>
+          <t>359294</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,67 +10726,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>261016</t>
+          <t>287873</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207779</t>
+          <t>263646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291511</t>
+          <t>313430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>613818</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>576823</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>652896</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>559313</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>483359</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>611701</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3073817</t>
+          <t>3112055</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3033477</t>
+          <t>3078706</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3138155</t>
+          <t>3141728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,67 +10839,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3312075</t>
+          <t>3344377</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3281580</t>
+          <t>3318820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3365312</t>
+          <t>3368604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>7576</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6456432</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6417354</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6493427</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>90,77%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>91,84%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>7576</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6385892</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6333504</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6461846</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3372114</t>
+          <t>3438000</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3372114</t>
+          <t>3438000</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3372114</t>
+          <t>3438000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573091</t>
+          <t>3632250</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573091</t>
+          <t>3632250</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573091</t>
+          <t>3632250</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6945205</t>
+          <t>7070250</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6945205</t>
+          <t>7070250</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6945205</t>
+          <t>7070250</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
